--- a/public/templates/문진업로드템플릿.xlsx
+++ b/public/templates/문진업로드템플릿.xlsx
@@ -1763,8 +1763,8 @@
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="E6:E47" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="응답유형 오류" error="SINGLE, MULTI, TEXT, NUMBER, DATE, SCALE 중에서 선택하세요." type="list">
-      <formula1>"SINGLE,MULTI,TEXT,NUMBER,DATE,SCALE"</formula1>
+    <dataValidation sqref="E6:E47" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="응답유형 오류" error="SINGLE, MULTI, SELECT, TEXT, TEXTAREA, NUMBER, DATE, BOOLEAN, SCALE, INFO, SIGNATURE 중에서 선택하세요." type="list">
+      <formula1>"SINGLE,MULTI,SELECT,TEXT,TEXTAREA,NUMBER,DATE,BOOLEAN,SCALE,INFO,SIGNATURE"</formula1>
     </dataValidation>
     <dataValidation sqref="G6:G47 I6:I47" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="입력 오류" error="Y 또는 N만 입력할 수 있습니다." type="list">
       <formula1>"Y,N"</formula1>
@@ -1780,7 +1780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1791,187 +1791,272 @@
     <row r="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>구분</t>
+          <t xml:space="preserve">구분</t>
         </is>
       </c>
       <c r="B1" s="11" t="inlineStr">
         <is>
-          <t>코드</t>
+          <t xml:space="preserve">코드</t>
         </is>
       </c>
       <c r="C1" s="11" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t xml:space="preserve">설명</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>응답유형</t>
+          <t xml:space="preserve">응답유형</t>
         </is>
       </c>
       <c r="B2" s="12" t="inlineStr">
         <is>
-          <t>SINGLE</t>
+          <t xml:space="preserve">SINGLE</t>
         </is>
       </c>
       <c r="C2" s="12" t="inlineStr">
         <is>
-          <t>단일 선택 (라디오버튼)</t>
+          <t xml:space="preserve">단일 선택 (라디오버튼)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>응답유형</t>
+          <t xml:space="preserve">응답유형</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>MULTI</t>
+          <t xml:space="preserve">MULTI</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>복수 선택 (체크박스)</t>
+          <t xml:space="preserve">복수 선택 (체크박스)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
         <is>
-          <t>응답유형</t>
+          <t xml:space="preserve">응답유형</t>
         </is>
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t xml:space="preserve">SELECT</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>주관식 텍스트</t>
+          <t xml:space="preserve">드롭다운 단일 선택</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>응답유형</t>
+          <t xml:space="preserve">응답유형</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t xml:space="preserve">TEXT</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>숫자 입력</t>
+          <t xml:space="preserve">주관식 짧은 텍스트(단답형)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>응답유형</t>
+          <t xml:space="preserve">응답유형</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t xml:space="preserve">TEXTAREA</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>날짜 선택</t>
+          <t xml:space="preserve">주관식 여러 줄 텍스트(장문형)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>응답유형</t>
+          <t xml:space="preserve">응답유형</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>SCALE</t>
+          <t xml:space="preserve">NUMBER</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>척도 (선택지에 최소|최대 기재)</t>
+          <t xml:space="preserve">숫자 입력</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>필수여부</t>
+          <t xml:space="preserve">응답유형</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t xml:space="preserve">DATE</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>필수 응답</t>
+          <t xml:space="preserve">날짜 선택</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>필수여부</t>
+          <t xml:space="preserve">응답유형</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>N</t>
+          <t xml:space="preserve">BOOLEAN</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>선택 응답</t>
+          <t xml:space="preserve">예/아니오 단일 체크</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>기타입력허용</t>
+          <t xml:space="preserve">응답유형</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t xml:space="preserve">SCALE</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>'기타(직접입력)' 옵션 추가</t>
+          <t xml:space="preserve">척도 (선택지에 최소|최대 기재, 예: 0|10)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>기타입력허용</t>
+          <t xml:space="preserve">응답유형</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>N</t>
+          <t xml:space="preserve">INFO</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>추가 안 함</t>
+          <t xml:space="preserve">입력 없는 안내 문구</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응답유형</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SIGNATURE</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서명 입력</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">필수여부</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">필수 응답</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">필수여부</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">선택 응답</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타입력허용</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'기타(직접입력)' 옵션 추가 (SINGLE/MULTI/SELECT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타입력허용</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">추가 안 함</t>
         </is>
       </c>
     </row>
